--- a/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_2.xlsx
+++ b/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,58 +567,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>echo2_sora_result_a</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ソラ:「三秒。返ってきた」</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Sora: 'Three seconds to come back.'</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Sora: 'Three seconds to come back.'</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>echo2_sora_result_b</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ソラ:「もう一度……今度は二秒だ」</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sora: 'Again... two seconds this time.'</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Sora: 'Again... two seconds this time.'</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_return");</t>
         </is>
       </c>
     </row>
@@ -630,130 +598,210 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>echo2_sora_logic</t>
+          <t>echo2_sora_result_a</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ソラ:「間隔が変わった。反射なら距離で決まるから、同じタイミングのはずだ」</t>
+          <t>ソラ:「三秒。返ってきた」</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Sora: 'The interval changed. If it's reflection, distance decides—and distance doesn't change.'</t>
+          <t>Sora: 'Three seconds to come back.'</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Sora: 'Three seconds to come back.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_return");</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>echo2_sora_result_b</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ソラ:「もう一度……今度は二秒だ」</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Sora: 'Again... two seconds this time.'</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Sora: 'Again... two seconds this time.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>echo2_sora_logic</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ソラ:「間隔が変わった。反射なら距離で決まるから、同じタイミングのはずだ」</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Sora: 'The interval changed. If it's reflection, distance decides—and distance doesn't change.'</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="G15" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sora: 'The interval changed. If it's reflection, distance decides—and distance doesn't change.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>echo2_mina_moved</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>ミナ:「お前が動いたんだろ」</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Mina: 'You moved.'</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Mina: 'You moved.'</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="G16" t="inlineStr">
+    <row r="20">
+      <c r="G20" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>echo2_sora_didnt</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>ソラ:「動いてない！ ……もう一回やる」</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Sora: 'I did not! ...I'm running it again.'</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Sora: 'I did not! ...I'm running it again.'</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="E19" t="inlineStr">
+    <row r="23">
+      <c r="E23" t="inlineStr">
         <is>
           <t>setFlag</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>chitsii.elinikki.quest.state.echo_experiment,2</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
+    <row r="24">
+      <c r="E24" t="inlineStr">
         <is>
           <t>fadeOut</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>0.3,black</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="E21" t="inlineStr">
+    <row r="25">
+      <c r="E25" t="inlineStr">
         <is>
           <t>setBG</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="E22" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
         <is>
           <t>end</t>
         </is>
